--- a/5W2H_aula20.xlsx
+++ b/5W2H_aula20.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dev_1o_Ano\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{98CAAFEE-034E-46F0-B6D4-B3D8242C79FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{77FF4C6F-A0F1-4165-9BD3-9C88F4256DEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8909ECCE-B8A2-4A8B-B440-EABBCC535D4A}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="8743" xr2:uid="{8909ECCE-B8A2-4A8B-B440-EABBCC535D4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+  <si>
+    <t>O que?</t>
+  </si>
   <si>
     <t>Por que?</t>
   </si>
@@ -59,36 +62,24 @@
     <t>Quanto?</t>
   </si>
   <si>
-    <t>5w2h</t>
-  </si>
-  <si>
-    <t>No local de aplicaçao da prova</t>
-  </si>
-  <si>
     <t>Para uma melhora na avaliaçao e educação do aluno, com o intuito de direcionar o aluno propriamente para sua area de profissional</t>
   </si>
   <si>
+    <t>Instituiçao: AEME e os alunos inscritos</t>
+  </si>
+  <si>
     <t>Sendo corrigido pelo avaliadores ou ia</t>
   </si>
   <si>
     <t>R$ 75 milhões por edição</t>
   </si>
   <si>
-    <t>Sempre no dia 11 de novembro a cada um ano</t>
-  </si>
-  <si>
-    <t>Para colocar mais pessoas na faculdade</t>
+    <t xml:space="preserve">Nas escolas </t>
   </si>
   <si>
     <t>AEME</t>
   </si>
   <si>
-    <t>Instituiçao: AEME e os alunos inscritos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nas escolas </t>
-  </si>
-  <si>
     <t>Periodo de ferias</t>
   </si>
   <si>
@@ -98,15 +89,6 @@
     <t xml:space="preserve">R$ 50 reais </t>
   </si>
   <si>
-    <t>Implementação de um sistema de reserva de vagas e convênios universitários</t>
-  </si>
-  <si>
-    <t>Para mudar o metodo de ensino do enem</t>
-  </si>
-  <si>
-    <t>porque ao inves de fazer uma prova teorica voce vai fazer o que gosta</t>
-  </si>
-  <si>
     <t>Nos locais informados no site da AEME</t>
   </si>
   <si>
@@ -116,23 +98,62 @@
     <t xml:space="preserve">No dia informado no site </t>
   </si>
   <si>
+    <t>Realizando a prova e tentando garatir um bom resultado</t>
+  </si>
+  <si>
     <t xml:space="preserve">uma vez por ano                                          </t>
   </si>
   <si>
-    <t>Realizando a prova e tentando garatir um bom resultado</t>
-  </si>
-  <si>
-    <t>O que?</t>
-  </si>
-  <si>
-    <t>Uma avaliação similar ao Exame Nacional do Ensino Médio (enem), que visa avaliar o aluno e melhorar a organização a nos estudos.</t>
+    <t>Reduzir a dependência da memorização mecânica dos conteúdos</t>
+  </si>
+  <si>
+    <t>5W2H</t>
+  </si>
+  <si>
+    <t>Sistemas educacionais integrados do estado</t>
+  </si>
+  <si>
+    <t>Professores da rede estadual</t>
+  </si>
+  <si>
+    <t>Uma avaliação similar ao Exame Nacional do Ensino Médio (enem), que visa avaliar o aluno e melhorar a organização a nos estudos, a fim de mostrar mais possibilidades de faculdades que sejam da area profissional dos estudantes</t>
+  </si>
+  <si>
+    <t>Aplicativos educacionais para estudo e acompanhamento</t>
+  </si>
+  <si>
+    <t>Implementação de um sistema de bolsa para faculdade, visto que há outras provas que não priorizam o interesse pessoal que a pessoa deseja estudar</t>
+  </si>
+  <si>
+    <t>Financiamento por recursos públicos do governo estadual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">por inscrição por alunoR$ 50 reais </t>
+  </si>
+  <si>
+    <t>Para colocar mais pessoas na faculdade, aumento de educação e mais profisionais qualificados dentro de suas áreas</t>
+  </si>
+  <si>
+    <t>porque ao inves de fazer uma prova teorica você pode se sentir mais confiante confortável, apresentando algo que tenha dominío</t>
+  </si>
+  <si>
+    <t>Para mudar o metodo de ensino do enem, a AEME lança um  novo projeto, no qual observar que cada área profissional tem suas matérias e conhecimentos mais importantes, sendo assim, é mais exigido em ambientes profisionais</t>
+  </si>
+  <si>
+    <t>No local de aplicação da prova</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Avaliações Personalizadas correspondentes a cada área que o aluno tenha mais finalidade</t>
+  </si>
+  <si>
+    <t>Sempre no dia 11 de dezenbro a cada um ano</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -141,6 +162,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="36"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -148,6 +178,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -155,7 +195,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -164,17 +204,75 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -187,9 +285,7 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -198,24 +294,24 @@
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -555,255 +651,155 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58CD62FD-F93C-4020-96C6-57A26BACA4B6}">
-  <dimension ref="A1:H17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="B1:H7"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="25.08984375" customWidth="1"/>
-    <col min="2" max="2" width="23.90625" customWidth="1"/>
-    <col min="3" max="3" width="21.6328125" customWidth="1"/>
-    <col min="4" max="4" width="22.81640625" customWidth="1"/>
-    <col min="5" max="5" width="22.6328125" customWidth="1"/>
-    <col min="6" max="6" width="19.81640625" customWidth="1"/>
-    <col min="7" max="7" width="18.90625" customWidth="1"/>
-    <col min="8" max="8" width="15.26953125" customWidth="1"/>
-    <col min="9" max="9" width="14.1796875" customWidth="1"/>
+    <col min="1" max="1" width="5.07421875" customWidth="1"/>
+    <col min="2" max="2" width="23.84375" customWidth="1"/>
+    <col min="3" max="3" width="21.53515625" customWidth="1"/>
+    <col min="4" max="4" width="22.84375" customWidth="1"/>
+    <col min="5" max="5" width="22.53515625" customWidth="1"/>
+    <col min="6" max="6" width="19.84375" customWidth="1"/>
+    <col min="7" max="7" width="19" customWidth="1"/>
+    <col min="8" max="8" width="15.3046875" customWidth="1"/>
+    <col min="9" max="9" width="14.15234375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="2:8" ht="21.55" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="E1" s="6"/>
+    </row>
+    <row r="2" spans="2:8" ht="62.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="3"/>
+    </row>
+    <row r="3" spans="2:8" ht="53.05" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
     </row>
-    <row r="2" spans="1:8" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+    <row r="4" spans="2:8" ht="156.55000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" ht="112.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="1"/>
+      <c r="C5" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="3" spans="1:8" ht="93" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+    <row r="6" spans="2:8" ht="135" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="4"/>
-    </row>
-    <row r="4" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" s="4"/>
-    </row>
-    <row r="5" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" s="4"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B2:H2"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1047,15 +1043,15 @@
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7103FA2A-C7EE-4415-8AA8-73D05B00ECEC}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="1aa2bcae-5fbf-4daa-bc30-8fd558065841"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1aa2bcae-5fbf-4daa-bc30-8fd558065841"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/5W2H_aula20.xlsx
+++ b/5W2H_aula20.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dev_1o_Ano\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dev_1o_Ano\Pictures\Screenshots\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{77FF4C6F-A0F1-4165-9BD3-9C88F4256DEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B3E383C-7663-4B32-8127-E5F7619D7219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="8743" xr2:uid="{8909ECCE-B8A2-4A8B-B440-EABBCC535D4A}"/>
   </bookViews>
